--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1425,508 +1425,508 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>The ONLY number that makes the VCU's milliamp command mean anything in the sim: T_wheel = I[A] * Kt * gear_ratio. At 0.2 the firmware's 125 A full-throttle command asks for 325 N*m per wheel, above the 273 N*m peak.</t>
+          <t>The ONLY number that makes the VCU's milliamp command mean anything in the sim: T_wheel = I[A] * Kt * gear_ratio. It also sets what 100% pedal is worth (max_motor_current below), so a wrong Kt scales every run's torque.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Pack voltage</t>
+          <t>Full-pedal motor current (firmware cap)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>V_DC</t>
+          <t>MAX_MOTOR_CURRENT_MA</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.pack_voltage</t>
+          <t>drivetrain.max_motor_current</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Accumulator (HV pack) nominal voltage.</t>
+          <t>Motor current the VCU commands at 100% pedal. The firmware's pedal map is linear to it.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (design decision 2026-08-30)</t>
+          <t>CURRENT CAR (powertrainControl.h MAX_MOTOR_CURRENT_MA, S-diff 5df1baf)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Nothing (design value)</t>
+          <t>Confirmation this is the intended full-throttle current, not a bring-up limit</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Accumulator design</t>
+          <t>dev/powertrainControl.h on the SRE-VCU S-diff branch</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x 20 kW at 380 V = 80 kW, which is EXACTLY the rules cap. That leaves the cap zero headroom, so it can never bind: the per-motor power limit is the operative constraint at every speed. See power_cap_total.</t>
+          <t>The firmware is the only controller, and it never asks for the motors' datasheet peak: 100% pedal is this current, through Kt and the gearbox. The driver adapter inverts the same map, so a maneuver's scripted torque is what the firmware actually commands. Mirrors the C #define; if the firmware changes it, change it here.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Motor peak power</t>
+          <t>Pack voltage</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>P_pk</t>
+          <t>V_DC</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.motor_power_peak</t>
+          <t>drivetrain.pack_voltage</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>20,000</t>
+          <t>Accumulator (HV pack) nominal voltage.</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>380</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED (kit curves scaled to 380 V)</t>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (design decision 2026-08-30)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Actual peak power at 380 V</t>
+          <t>Nothing (design value)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
+          <t>Accumulator design</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. Four motors top out at 80 kW — numerically identical to the rules cap, so THIS per-motor limit is what actually binds, not the cap.</t>
+          <t>Not used directly by the physics — it SETS motor peak power below. 4 motors x 20 kW at 380 V = 80 kW, which is EXACTLY the rules cap. That leaves the cap zero headroom, so it can never bind: the per-motor power limit is the operative constraint at every speed. See power_cap_total.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Motor max speed</t>
+          <t>Motor peak power</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>n_max</t>
+          <t>P_pk</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.motor_max_speed</t>
+          <t>drivetrain.motor_power_peak</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Maximum motor shaft speed.</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>2,094</t>
+          <t>Peak mechanical power of ONE motor at OUR pack voltage.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as 20,000 rpm)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (AMK kit datasheet)</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED (kit curves scaled to 380 V)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Nothing (datasheet value)</t>
+          <t>Actual peak power at 380 V</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>AMK kit manual 6.5.3 (characteristics end at 20,000 rpm)</t>
+          <t>Read the 380 V curve in the AMK manual; dyno pull once the pack exists</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter. NOT enforced by this basic sim; recorded for completeness and future top-speed studies.</t>
+          <t>Caps torque above ~17 m/s (37 mph): at 40 mph only 256 of 273 N*m is available. Four motors top out at 80 kW — numerically identical to the rules cap, so THIS per-motor limit is what actually binds, not the cap.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Wheel spin inertia, rear corner</t>
+          <t>Motor max speed</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>I_w,r</t>
+          <t>n_max</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.I_wheel_rear</t>
+          <t>drivetrain.motor_max_speed</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Spin inertia of ONE REAR corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>Maximum motor shaft speed.</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2,094</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>kg*m^2</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>DERIVED estimate — replace with CAD</t>
+          <t>rad/s (entered as 20,000 rpm)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (AMK kit datasheet)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Rotating inertia of one rear corner</t>
+          <t>Nothing (datasheet value)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
+          <t>AMK kit manual 6.5.3 (characteristics end at 20,000 rpm)</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes. Together with I_wheel_front it also sets the effective mass the car must accelerate, which verify.py D1 measures against a closed-form coast-down.</t>
+          <t>~36 m/s (80 mph) ground speed at 13:1 — comfortably above the 40 mph envelope, not the limiter. NOT enforced by this basic sim; recorded for completeness and future top-speed studies.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Wheel spin inertia, rear corner</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>I_w,r</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.I_wheel_rear</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Spin inertia of ONE REAR corner about the axle: tire + rim + brake rotor + hub + (motor rotor inertia * gear_ratio^2).</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>kg*m^2</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>DERIVED estimate — replace with CAD</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Rotating inertia of one rear corner</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CAD mass properties + rotor J from the exact AMK motor sheet</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Sets how fast an unloaded wheel spins up — the s-diff's whole problem. Controller gains are sensitive to it: retune when it changes. Together with I_wheel_front it also sets the effective mass the car must accelerate, which verify.py D1 measures against a closed-form coast-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>Wheel spin inertia, front corner</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>I_w,f</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>drivetrain.I_wheel_front</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Spin inertia of ONE FRONT corner about the axle. Same construction as the rear — same tire, same rim, same in-upright motor and planetary, same brake rotor — so the same number, written as a formula so the ASSUMPTION is visible in the data rather than buried in code.</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>kg*m^2</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>DERIVED — front corner ASSUMED identical to rear; replace when CAD says otherwise</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Rotating inertia of one front corner (CAD)</t>
         </is>
       </c>
-      <c r="I26" s="3">
+      <c r="I27" s="3">
         <f> drivetrain.I_wheel_rear</f>
         <v/>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>The front rotor spins whether or not that motor is energised, so this number is real for the 2-rear build too. It is the term the sim dropped when it called the fronts "massless free-rollers": worth 2*I/r_w^2 = 13.4 kg of apparent mass, 5.3% of the car, and 0.6% on a 3 s coast-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Total power cap</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>P_max</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>drivetrain.power_cap_total</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE (simplified)</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Nothing (rulebook)</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Confirm in the current-year rulebook</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier. PRESENTLY UNREACHABLE: driven_wheels * motor_power_peak == this value exactly, so the per-motor clip already implies it and the total-cap branch is dead code (verify F16 reports the zero headroom). It becomes live the moment motor_power_peak is revised upward — that number is DERIVED from kit curves by three methods spanning 18.1-20.3 kW — or if driveline losses are ever modelled, since the rules limit is electrical at the accumulator while this one is applied to mechanical power.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Driven wheels</t>
+          <t>Total power cap</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>n_drv</t>
+          <t>P_max</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>drivetrain.driven_wheels</t>
+          <t>drivetrain.power_cap_total</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>How many wheels receive drive torque. 4 = one motor per upright; 2 = the rear pair only, which is what the current build runs.</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>FSAE EV rules limit on total drive power (EV.4.2, 80 kW at the accumulator).</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>80,000</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (four motors fitted, one per upright)</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (simplified)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Which inverters are commissioned on the car</t>
+          <t>Nothing (rulebook)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Powertrain: count enabled inverters</t>
+          <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>The scale between "peak torque at ONE wheel" and "peak torque the driver can ask for". Every axle-torque budget in the sim is n_drv * T_wheel_max: the maneuver throttle steps, the APPS pedal map, the driver adapter's exact inverse of it, and the plot ceilings.</t>
+          <t>Hard ceiling. The sim applies it to mechanical power (no drivetrain losses modeled) — the real car hits it ~10-15% earlier. PRESENTLY UNREACHABLE: driven_wheels * motor_power_peak == this value exactly, so the per-motor clip already implies it and the total-cap branch is dead code (verify F16 reports the zero headroom). It becomes live the moment motor_power_peak is revised upward — that number is DERIVED from kit curves by three methods spanning 18.1-20.3 kW — or if driveline losses are ever modelled, since the rules limit is electrical at the accumulator while this one is applied to mechanical power.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>Driven wheels</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>n_drv</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>drivetrain.driven_wheels</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>How many wheels receive drive torque. 4 = one motor per upright; 2 = the rear pair only, which is what the current build runs.</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (four motors fitted, one per upright)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Which inverters are commissioned on the car</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Powertrain: count enabled inverters</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>The scale between "peak torque at ONE wheel" and "peak torque the driver can ask for". Every axle-torque budget in the sim is n_drv * T_wheel_max: the maneuver throttle steps, the APPS pedal map, the driver adapter's exact inverse of it, and the plot ceilings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>Regen speed cutoff</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>drivetrain.regen_speed_cutoff</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Below this speed no negative (regen) torque is commanded.</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>m/s (~5 km/h)</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>RULES VALUE (approx.)</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Nothing (rulebook)</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Confirm in the current-year rulebook</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Rules restrict regen near standstill; also keeps the sim's low-speed slip math out of its untrustworthy zone.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>AERO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Lift coefficient</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>C_L</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>aero.cl_coeff</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT (old car's aero)</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Current car's downforce coefficient</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>CFD, then straight-line coast-down / load-cell validation</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient</t>
+          <t>Lift coefficient</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>C_D</t>
+          <t>C_L</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>aero.cd_coeff</t>
+          <t>aero.cl_coeff</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Drag coefficient, same reference area.</t>
+          <t>Lift (downforce) coefficient, referenced to frontal_area.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1941,368 +1941,368 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Current car's drag coefficient</t>
+          <t>Current car's downforce coefficient</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>CFD + coast-down test</t>
+          <t>CFD, then straight-line coast-down / load-cell validation</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
+          <t>Downforce = 0.5*rho*C_L*A*v^2 — free grip that grows with speed^2.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Frontal area</t>
+          <t>Drag coefficient</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>A_F</t>
+          <t>C_D</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>aero.frontal_area</t>
+          <t>aero.cd_coeff</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Aerodynamic frontal reference area.</t>
+          <t>Drag coefficient, same reference area.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>m^2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>FROM REPORT</t>
+          <t>FROM REPORT (old car's aero)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Projected frontal area</t>
+          <t>Current car's drag coefficient</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>CAD projection</t>
+          <t>CFD + coast-down test</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+          <t>Sets top-speed force budget and the torque needed to hold speed in every maneuver.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>Frontal area</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>A_F</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>aero.frontal_area</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Aerodynamic frontal reference area.</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>1.106</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>m^2</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Projected frontal area</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>CAD projection</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Only the products C*A enter the physics — keep coefficient and area consistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>ClA (computed)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>C_L*A</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>aero.ClA</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>The downforce product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>3.517</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="3">
+      <c r="I35" s="3">
         <f> aero.cl_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>CdA (computed)</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>C_D*A</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>aero.CdA</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>The drag product the sim actually uses.</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>1.504</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>m^2</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="3">
+      <c r="I36" s="3">
         <f> aero.cd_coeff * aero.frontal_area</f>
         <v/>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Aero balance</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>pct_aero_f</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>aero.balance_front</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Fraction of total downforce landing on the FRONT axle (0.45 = 45/55).</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — pure guess</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Center-of-pressure position</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>CFD (aero team) — ask for CP height too</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Moves grip between axles as speed rises — shapes high-speed balance directly. One of the last pure guesses outside tires.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>STEERING GEOMETRY</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Ackermann fraction</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>pct_A</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>steering.ackermann_fraction</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>How much of the geometric (100%) Ackermann inner/outer steer split the steering actually delivers. 0.0 = parallel steer (both fronts get the same angle), 1.0 = full geometric Ackermann, negative = anti-Ackermann.</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER (parallel) — RWheel curve needed</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>The steering curve: both wheels' angles vs handwheel angle</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>From the steering chart: the LWheel curve is on file, need the RWheel polynomial from the same chart (or a few x, LWheel, RWheel point triples).</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Only matters at large steer angles: at 5 deg the split is ~+/-0.2 deg; at the 23 deg full-lock hairpin it is ~+/-4 deg per wheel. Proven to flip whether s-diff-only survives the hairpin (runs 007 vs 008).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>LOAD TRANSFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Front spring rate</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ks_f</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>loads.spring_rate_front</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>N/mm (ratio only)</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>FROM REPORT</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Front roll stiffness incl. ARBs and motion ratios</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Suspension team</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Rear spring rate</t>
+          <t>Front spring rate</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>ks_r</t>
+          <t>ks_f</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>loads.spring_rate_rear</t>
+          <t>loads.spring_rate_front</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+          <t>Front suspension spring rate. Used ONLY through its ratio to the rear.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+          <t>Front roll stiffness incl. ARBs and motion ratios</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2327,144 +2327,144 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Denominator half of the lateral load-transfer split.</t>
+          <t>Numerator of the lateral load-transfer split.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>Rear spring rate</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>ks_r</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>loads.spring_rate_rear</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Rear suspension spring rate. Used ONLY through its ratio to the front.</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>N/mm (ratio only)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>FROM REPORT</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Rear roll stiffness incl. ARBs and motion ratios</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Suspension team</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Denominator half of the lateral load-transfer split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>Front lateral-transfer fraction</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>loads.lat_transfer_frac_front</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Share of total LATERAL load transfer reacted by the FRONT axle, set by the front/rear roll-stiffness split.</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>0.4376</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>FROM REPORT (spring-rate ratio only) — crude</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Front vs rear roll stiffness</t>
         </is>
       </c>
-      <c r="I42" s="3">
+      <c r="I43" s="3">
         <f> loads.spring_rate_front / (loads.spring_rate_front + loads.spring_rate_rear)</f>
         <v/>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Which axle eats the load transfer = which axle loses grip first — trades understeer/oversteer at the limit.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>TIRES — TTC ROUND 9 FIT (R20 compound, 2026-08-31); surrogate sizes, road µ = belt × 0.67 pending skidpad</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Belt→road grip scale</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>tires.mu_road_scale</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — skidpad measures this</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Steady-state skidpad lateral g</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Skidpad test vs sim prediction</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, lateral</t>
+          <t>Belt→road grip scale</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_y</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_lat</t>
+          <t>tires.mu_road_scale</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>2.593</t>
+          <t>Belt-&gt;asphalt grip scaling. Calspan's sandpaper belt grips harder than track asphalt; common practice scales the fitted peak mu by ~0.65-0.70 for on-road prediction (stiffnesses/shapes carry over unscaled).</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2472,51 +2472,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — skidpad measures this</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Steady-state skidpad lateral g</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
+          <t>Skidpad test vs sim prediction</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+          <t>Multiplies EVERY grip number — the single biggest absolute-accuracy lever left. VALIDATE on skidpad; that measurement replaces this guess with truth.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Belt peak µ, longitudinal</t>
+          <t>Belt peak µ, lateral</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>mu_belt_x</t>
+          <t>mu_belt_y</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>tires.belt_mu_long</t>
+          <t>tires.belt_mu_lat</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+          <t>Peak LATERAL friction coefficient as fitted on the Calspan belt.</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2.593</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>tire_fit.py on Round 9 drive/brake runs</t>
+          <t>tire_fit.py on Round 9 cornering runs (surrogate spread +/-6%)</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2548,279 +2548,279 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>Belt peak µ, longitudinal</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>mu_belt_x</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>tires.belt_mu_long</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Peak LONGITUDINAL friction coefficient as fitted on the belt.</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>2.359</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>tire_fit.py on Round 9 drive/brake runs</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Scaled by mu_road_scale to give the road value the sim uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
           <t>Peak friction coefficient</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>mu0</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>tires.mu0</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Peak grip per newton of load, at the nominal load (road value).</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>1.737</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Peak mu at several loads</t>
         </is>
       </c>
-      <c r="I47" s="3">
+      <c r="I48" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_lat</f>
         <v/>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>THE grip number. Max lateral g, spin thresholds, everything — the single most important number in the sim.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Peak longitudinal friction</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>mu0x</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>tires.mu0_long</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Drive/brake grip peak — fitted 9% below lateral; combined slip caps on the friction ELLIPSE in tire.py.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>1.581</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="3">
+      <c r="I49" s="3">
         <f> tires.mu_road_scale * tires.belt_mu_long</f>
         <v/>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Sets wheelspin threshold and traction capability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>s_mu</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>tires.s_mu</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>0.112</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>—/100% load</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>mu at low vs high load</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>Same TTC fit</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>Load sensitivity</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>s_mu</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>tires.s_mu</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Load sensitivity — how much the friction COEFFICIENT drops as vertical load rises: mu = mu0 * (1 - s_mu*(Fz/Fz_nom - 1)). Shared by the lateral and longitudinal peaks.</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>—/100% load</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>mu at low vs high load</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Same TTC fit</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>The reason load transfer costs grip and torque placement matters at all. Zero would make TV pointless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>Nominal tire load</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Fz_nom</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>tires.Fz_nom</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>The "nominal" vertical load at which mu0 is defined (~one static corner weight).</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>618.6</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>DERIVED (follows the masses automatically)</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="3">
+      <c r="I51" s="3">
         <f> (mass.car_no_driver + mass.driver) * environment.g / 4.0</f>
         <v/>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Reference point for the load-sensitivity line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Front cornering stiffness</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>c_alpha_f</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>tires.c_alpha_front</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>1/rad</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>TTC FIT R9 (same tire all round)</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>Slope of Fy vs slip angle at small angles</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>TTC cornering sweep</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Rear cornering stiffness</t>
+          <t>Front cornering stiffness</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>c_alpha_r</t>
+          <t>c_alpha_f</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>tires.c_alpha_rear</t>
+          <t>tires.c_alpha_front</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Same, for a REAR tire.</t>
+          <t>Normalized cornering stiffness of a FRONT tire: lateral force per radian of slip angle, per newton of load (C_alpha = this * Fz).</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Same, rear</t>
+          <t>Slope of Fy vs slip angle at small angles</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -2850,91 +2850,91 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Rear grip slope — stability side of the understeer gradient.</t>
+          <t>Front-axle responsiveness; with rear stiffness sets the understeer gradient K_us the TV reference uses.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal slip stiffness</t>
+          <t>Rear cornering stiffness</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>c_kappa</t>
+          <t>c_alpha_r</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>tires.c_kappa</t>
+          <t>tires.c_alpha_rear</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
+          <t>Same, for a REAR tire.</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>1/slip</t>
+          <t>1/rad</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>TTC FIT R9</t>
+          <t>TTC FIT R9 (same tire all round)</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Slope of Fx vs slip ratio</t>
+          <t>Same, rear</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>TTC drive/brake sweep</t>
+          <t>TTC cornering sweep</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
+          <t>Rear grip slope — stability side of the understeer gradient.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Lateral shape factor</t>
+          <t>Longitudinal slip stiffness</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>C_y</t>
+          <t>c_kappa</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_lat</t>
+          <t>tires.c_kappa</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
+          <t>Normalized longitudinal slip stiffness: drive/brake force per unit slip ratio per newton (C_kappa = this * Fz).</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/slip</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -2944,44 +2944,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Curve shape near/past the peak</t>
+          <t>Slope of Fx vs slip ratio</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>TTC fit</t>
+          <t>TTC drive/brake sweep</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
+          <t>Sets wheel-spin dynamics speed — the s-diff's plant. Gains retune if it moves.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Lateral curvature factor</t>
+          <t>Lateral shape factor</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>E_y</t>
+          <t>C_y</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>tires.curv_e_lat</t>
+          <t>tires.shape_c_lat</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
+          <t>Magic Formula shape factor — how sharply lateral force peaks.</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Post-peak behavior</t>
+          <t>Curve shape near/past the peak</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
+          <t>With E_y, sets where the curve peaks (currently 11.6 deg — real slicks ~6-10 deg) and how it lets go.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Longitudinal shape factor</t>
+          <t>Lateral curvature factor</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>C_x</t>
+          <t>E_y</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>tires.shape_c_long</t>
+          <t>tires.curv_e_lat</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Same idea, drive/brake direction.</t>
+          <t>Magic Formula curvature factor — fall-off past the lateral peak.</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Curve shape</t>
+          <t>Post-peak behavior</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3058,125 +3058,125 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+          <t>Gentle vs snappy breakaway — currently more forgiving than a real slick.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>Longitudinal shape factor</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>C_x</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>tires.shape_c_long</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Same idea, drive/brake direction.</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>1.705</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>TTC FIT R9</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Curve shape</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>TTC fit</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Sets the peak slip ratio (~0.10) — also the replay's red-wheel spin threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
           <t>Longitudinal curvature factor</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>E_x</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>tires.curv_e_long</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Fall-off past the longitudinal peak.</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>0.389</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>TTC FIT R9</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Post-peak behavior</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>TTC fit</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>How violently a spinning wheel loses force — feeds the wheelspin runaway.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>SENSORS &amp; VCU — the VCU itself</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>VCU loop rate</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>sensors.vcu.rate_hz</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — ask software team</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>The real VCU loop rate</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Software team</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Plausibility cut threshold</t>
+          <t>VCU loop rate</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3186,49 +3186,49 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_cut</t>
+          <t>sensors.vcu.rate_hz</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage above which, while braking, motor power must be cut.</t>
+          <t>VCU control-loop rate — how often sensors are sampled and torque commands are recomputed (physics still integrates at 4 kHz).</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>RULES VALUE (EV.4.7)</t>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — ask software team</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The real VCU loop rate</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Rulebook (confirm current year)</t>
+          <t>Software team</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
+          <t>Gains proven stable at 100 Hz (verify.py section H); make it match reality before quoting controller performance.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Plausibility restore threshold</t>
+          <t>Plausibility cut threshold</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.plaus_apps_restore</t>
+          <t>sensors.vcu.plaus_apps_cut</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>APPS percentage the pedal must fall below before power is restored.</t>
+          <t>APPS percentage above which, while braking, motor power must be cut.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>The latch that makes the cut a latch and not a flicker.</t>
+          <t>Implemented and unit-tested (verify I3); the pedal_check maneuver demonstrates it.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Sensor noise seed</t>
+          <t>Plausibility restore threshold</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3290,79 +3290,79 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.seed</t>
+          <t>sensors.vcu.plaus_apps_restore</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
+          <t>APPS percentage the pedal must fall below before power is restored.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>RULES VALUE (EV.4.7)</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD (repeatability)</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rulebook (confirm current year)</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Fair comparisons and reproducible runs.</t>
+          <t>The latch that makes the cut a latch and not a flicker.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>vx estimator time constant</t>
+          <t>Sensor noise seed</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>tau_vx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>sensors.vcu.vx_tau</t>
+          <t>sensors.vcu.seed</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>How fast the wheel-speed measurement pulls the ground-speed estimate.</t>
+          <t>Seed for the sensor-noise generator — runs are exactly repeatable and all four controller configs see IDENTICAL noise.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>TUNED (sim)</t>
+          <t>NUMERICAL GUARD (repeatability)</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -3372,189 +3372,189 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Corner exit at high throttle — shortest tau that still rides out a spin event</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>Short enough that the estimate cannot drift far on the accelerometer alone, long enough that one quantization LSB of wheel speed does not shake the slip ratios a traction guard reads. Applied as dt/(dt+tau), so the filter behaves identically at the 100 Hz VCU rate and the 4 kHz rate verify I4 uses.</t>
+          <t>Fair comparisons and reproducible runs.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>vx estimator time constant</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>tau_vx</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>sensors.vcu.vx_tau</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>How fast the wheel-speed measurement pulls the ground-speed estimate.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>TUNED (sim)</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Corner exit at high throttle — shortest tau that still rides out a spin event</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Short enough that the estimate cannot drift far on the accelerometer alone, long enough that one quantization LSB of wheel speed does not shake the slip ratios a traction guard reads. Applied as dt/(dt+tau), so the filter behaves identically at the 100 Hz VCU rate and the 4 kHz rate verify I4 uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
           <t>Wheel-speed scatter reference</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>sensors.vcu.vx_spread_ref</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Spread between fastest and slowest wheel (as ground speed) at which the estimator stops trusting the wheels and coasts on the accelerometer.</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>TUNED (sim)</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>Track tests — the largest HONEST spread that corner geometry produces</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>With four DRIVEN wheels there is no undriven reference left: under power every wheel over-reads, so min(w)*r_wheel is no longer a lower bound on ground speed. Scatter is the signal that says "some corner is slipping". 1.5 m/s sits above the r*track difference real cornering produces (about 0.6 m/s at 1 rad/s) and below a genuine spin event.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>SENSORS — APPS, accelerator pedal position</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>APPS quantization</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>sensors.throttle_pos.quant_pct</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Accelerator pedal position resolution.</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>%/LSB</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>APPS sensor spec</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Datasheet</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>Torque request granularity.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SENSORS — BPS, brake pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>BPS full range</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>sensors.brake_pressure_sens.range_bar</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Brake pressure sensor full range.</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — sensor spec</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>BPS spec + brake system pressures</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>Brake team: line pressure at threshold/full braking</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>BPS quantization</t>
+          <t>BPS full range</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.quant_bar</t>
+          <t>sensors.brake_pressure_sens.range_bar</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Brake pressure sensor resolution.</t>
+          <t>Brake pressure sensor full range.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>bar/LSB</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -3589,24 +3589,24 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>BPS spec</t>
+          <t>BPS spec + brake system pressures</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Brake team: line pressure at threshold/full braking</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Regen command granularity.</t>
+          <t>Sets the pressure that maps to full regen.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>BPS actuated threshold</t>
+          <t>BPS quantization</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3616,244 +3616,244 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>sensors.brake_pressure_sens.actuated_bar</t>
+          <t>sensors.brake_pressure_sens.quant_bar</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+          <t>Brake pressure sensor resolution.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>bar/LSB</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — calibration choice</t>
+          <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Brake system pressures</t>
+          <t>BPS spec</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Brake team: line pressure at threshold braking</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+          <t>Regen command granularity.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>BPS actuated threshold</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>sensors.brake_pressure_sens.actuated_bar</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Pressure above which the brake counts as "actuated" for the rules check.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — calibration choice</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Brake system pressures</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Brake team: line pressure at threshold braking</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Defines "braking" for the EV.4.7 plausibility check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>Max regen torque</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>sensors.brake_pressure_sens.t_regen_max</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Total REGEN torque at full brake pressure, across ALL driven wheels.</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>N*m</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — battery charge limit sets this</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Allowed charge current -&gt; torque</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>Accumulator team: max charge C-rate</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>Caps how much "braking" the sim's BPS can command.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>SENSORS — WSS, motor resolver over CAN</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>WSS quantization</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>sensors.wheel_speed.quant_rpm</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Motor-speed resolution over CAN (motor side, before the planetary divide).</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>rpm/LSB</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — AMK CAN resolution</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>AMK CAN speed resolution</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>AMK CAN spec</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>1 motor rpm is about 1.8 mm/s of ground speed — the resolver-over-CAN path is effectively noise-free wheel speed.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>SENSORS — SAS, steering angle, and the steering map</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Steering map A0 (intercept)</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>A0</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>sensors.steering_angle.map_a0</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>-0.0797</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>deg (intercept)</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (team chart)</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>The steering curve including RWheel</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>Steering chart / kinematics sweep</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Steering map A1 (linear)</t>
+          <t>Steering map A0 (intercept)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a1</t>
+          <t>sensors.steering_angle.map_a0</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Linear term — the near-center steering ratio.</t>
+          <t>Constant term of the handwheel -&gt; road-wheel polynomial.</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.0797</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>deg/deg</t>
+          <t>deg (intercept)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -3873,44 +3873,44 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
+          <t>Subtracted out to center the map; kept so the raw fit stays visible.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Steering map A2 (quadratic)</t>
+          <t>Steering map A1 (linear)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>sensors.steering_angle.map_a2</t>
+          <t>sensors.steering_angle.map_a1</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Quadratic term — the ratio falling off toward lock.</t>
+          <t>Linear term — the near-center steering ratio.</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>-0.000844</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>deg/deg^2</t>
+          <t>deg/deg</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+          <t>CURRENT CAR (team chart)</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -3925,155 +3925,155 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+          <t>How the VCU turns the SAS reading into a road-wheel angle.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
+          <t>Steering map A2 (quadratic)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>sensors.steering_angle.map_a2</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Quadratic term — the ratio falling off toward lock.</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>-0.000844</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>deg/deg^2</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (team chart; -844E-04 read as -8.44E-04)</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>The steering curve including RWheel</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Steering chart / kinematics sweep</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Full lock 23 deg is about 103 deg of handwheel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
           <t>SAS quantization</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>sensors.steering_angle.quant_deg</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Steering-angle sensor resolution, at the handwheel.</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>deg/LSB</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — sensor spec</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>Sensor spec</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>Datasheet of the chosen SAS</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>Steering resolution the VCU actually sees.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>SENSORS — IMU, yaw gyro and accelerometers</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>IMU gyro noise (1σ)</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>sigma_g</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>sensors.imu_6axis.gyro_noise_std</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>0.005236</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>rad/s (entered as deg/s, 1 sigma)</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — IMU spec</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>IMU datasheet numbers</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>Chosen IMU's spec sheet</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>IMU gyro bias</t>
+          <t>IMU gyro noise (1σ)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>b_g</t>
+          <t>sigma_g</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.gyro_bias</t>
+          <t>sensors.imu_6axis.gyro_noise_std</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Constant yaw-gyro zero offset.</t>
+          <t>Yaw-gyro 1-sigma noise.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>0.001745</t>
+          <t>0.005236</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>rad/s (entered as deg/s)</t>
+          <t>rad/s (entered as deg/s, 1 sigma)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
+          <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -4083,1402 +4083,348 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+          <t>Chosen IMU's spec sheet</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Biases the yaw-rate error the TV controller integrates.</t>
+          <t>Goes straight into the TV feedback — sets how clean the yaw control can be.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>VCU gyro low-pass</t>
+          <t>IMU gyro bias</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>f_c</t>
+          <t>b_g</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>sensors.imu_6axis.lpf_hz</t>
+          <t>sensors.imu_6axis.gyro_bias</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+          <t>Constant yaw-gyro zero offset.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.001745</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>rad/s (entered as deg/s)</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — VCU filter choice</t>
+          <t>PLACEHOLDER — uncalibrated bias</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IMU datasheet numbers</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Software choice; tune against noise</t>
+          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+          <t>Biases the yaw-rate error the TV controller integrates.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>VCU gyro low-pass</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>f_c</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>sensors.imu_6axis.lpf_hz</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>First-order low-pass the VCU applies to the gyro before feedback.</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — VCU filter choice</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Software choice; tune against noise</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Trade: more filtering = less dither but more phase lag in the yaw loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>IMU accel noise</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>sigma_a</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>sensors.imu_6axis.accel_noise_std</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>m/s^2</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>PLACEHOLDER — IMU spec</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>IMU datasheet</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>Spec sheet</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>Feeds future estimation (vx observer, validation logging).</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>CONTROLLER CONSTANTS — open-loop s-diff, mirrored from sdiff.c</t>
-        </is>
-      </c>
-    </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Steering ratio (handwheel : road-wheel)</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>STEERING_RATIO</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>controllers.steering_ratio</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Divides handwheel angle down to road-wheel angle in sdiff.c.</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c STEERING_RATIO)</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>Team steering chart (sensors/steering_angle/params.yaml, A1 term)</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors the C constant. NOT used by the Python controller — the sim gets its road-wheel angle from the SAS polynomial map in model/sensors/steering_angle/sas.py, which implies ~3.2:1 near center and ~7.5:1 at lock. The flat 5.4 here and that map disagree; the map is the more accurate model of the real linkage.</t>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Steer angle at full derate</t>
+          <t>SIL firmware boot time</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>DELTA_MAX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>controllers.delta_max</t>
+          <t>sil.boot_s</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Normalizes steer angle to 0-1 in sdiff.c (delta_norm), clamped at 1.</t>
+          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>0.03491</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>SUSPECT — mirrors sdiff.c DELTA_MAX, but see note</t>
+          <t>PLACEHOLDER — from main.c / initializations.c</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Confirmation from the VCU team that 2 deg is intended (see note)</t>
+          <t>The firmware's true settle time</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
+          <t>Read main.c / initializations.c, or instrument the boot</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>NOT full lock — this is the angle at which the derate SATURATES. At 2 deg of road wheel (about 10.8 deg of handwheel at 5.4:1) delta_norm hits 1.0 and the inner-wheel cut is already at its maximum, so the s-diff behaves close to on/off rather than progressive.</t>
+          <t>Too short and the first samples come from an unsettled ADC.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Friction-budget derate gain</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>K_DERATE</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>controllers.k_derate</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>How much total torque (both wheels) falls off as steer angle rises.</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c K_DERATE)</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>Deliberately zeroed in commit 18f9bc7 before the first on-car run: the shared budget cut is OFF, so f = 1.0 always and f_min below is inert. The s-diff currently biases left/right without taking any total power away.</t>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARDS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Inner-wheel derate gain</t>
+          <t>Low-speed guard</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>K_INNER</t>
+          <t>v_eps</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>controllers.k_inner</t>
+          <t>numerical.v_eps</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Torque cut applied to the inner (unloaded) wheel, scaled by delta_norm.</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>0.42</t>
+          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c K_INNER, tuned on car)</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>Tuned on car across the PNR sessions</t>
-        </is>
-      </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>The whole point of the s-diff: keep the inner wheel from spinning up. At full delta_norm the inner wheel gets 58% of the base torque. This is the ONE constant with real on-car provenance — 0.35 (run #1) -&gt; 0.45 (run #2, 3bd6d88) -&gt; 0.42 (run #3, 5df1baf).</t>
+          <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Friction-budget floor</t>
+          <t>Wheel-speed guard</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F_MIN</t>
+          <t>w_eps</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>controllers.f_min</t>
+          <t>numerical.w_eps</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Lowest the shared (both-wheel) torque multiplier can fall to.</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>0.5</t>
+          <t>Floor on |wheel speed| when converting a per-motor POWER limit into a torque limit (T_lim = P_peak / max(|omega|, w_eps)).</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>NUMERICAL GUARD</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Nothing (numerical)</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c F_MIN)</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
-        </is>
-      </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Floors the k_derate budget cut. INERT while k_derate = 0 — f never leaves 1.0, so this clamp is never reached. It matters again the moment anyone turns the shared derate back on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Steering deadband</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>DEADBAND</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>controllers.deadband</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Road-wheel angle band around center treated as "straight" (no split).</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>0.01745</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c DEADBAND)</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>Stops the inner/outer split from chattering when the driver is nominally straight. 1 deg of road wheel is about 5.4 deg of handwheel, comfortably above the SAS quantization (0.5 deg at the handwheel).</t>
+          <t>P = T*omega, so at standstill the power limit permits infinite torque. Flooring the divisor caps it at P_peak/w_eps instead, which the per-wheel peak-torque limit then covers. 5 rad/s is ~1.1 m/s of ground speed, below the regen cutoff, so it never binds while the car is actually driving.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Slew rate</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>RATE</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>controllers.rate</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Max speed the friction-budget and left/right multipliers may change, per second.</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT CAR (sdiff.c RATE)</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>dev/sdiff.c on the S-diff branch</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>Without slew limiting, torque would jump discontinuously at the deadband edges. At 1.0/s the full 0.42 inner cut takes 0.42 s to apply — far slower than any sensor or loop latency in the stack, which is why loop delay is not modeled here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>CONTROLLER — four-corner torque allocator (AWD, sim design output)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Base front torque share</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>frac_f0</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.frac_front_base</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Front-axle share of total drive torque before any load-transfer correction.</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>A front/rear bias decision from the powertrain team</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>Start near geometry.weight_fraction_front (0.4344), then sweep in the corner tests</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>With k_load = 1 this is the whole split at zero acceleration. Slightly ABOVE the static front weight fraction on purpose: mu rises as load falls, so the lightly loaded front axle makes a little more grip per newton than its load share implies (0.8 points at rest, 2.3 at 1.2 g). This offset absorbs most of that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Load-following gain</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>K_LOAD</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.k_load</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>How strongly the axle split follows the estimated normal-load split.</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>Sweep 0 -&gt; 1 across corner_exit and the track matrix</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>frac_front = frac_front_base + k_load*(Fz_front_share - static_front_share). 1.0 = torque tracks axle load; 0 = a fixed split that ignores load transfer. The front share falls 0.434 -&gt; 0.283 at 1 g, so this gain moves ~15 points of the split. It is the biggest single lever in the allocator, and the reason it exists: an even four-way split spins the fronts above ~500 N*m of request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>Front share floor</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.frac_front_min</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Lowest front-axle torque share the allocator may command.</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>Set above zero so the front inverters never fully idle mid-corner</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>At 1.5 g the load estimate alone asks for 0.21, so this floor is not normally active. It exists so a bad ax estimate can never fully unload the front motors, which would make their resolver speeds useless to the spin guard and to the ground-speed estimator that depends on all four corners disagreeing honestly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>Front share ceiling</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.frac_front_max</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Highest front-axle torque share the allocator may command.</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>Corner tests; the binding case is regen, not drive</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>The front tires are also making the car's steering force, so their longitudinal budget is smaller than a pure load estimate implies. Under regen the load moves forward and the raw estimate asks for more than this, so this ceiling is the one that actually binds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>Axle-split slew rate</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.frac_rate</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Maximum rate of change of the front torque share, per second.</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>Fast enough not to lag a throttle step, slow enough not to step the actuators</t>
-        </is>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>The load estimate follows the torque REQUEST, which the driver can step. Slewing the share (the same slew() the s-diff uses) keeps a pedal step from stepping the front/rear split. At 2.0/s a full 0.44 -&gt; 0.10 swing takes 0.17 s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Feedforward accel clamp</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.ax_est_max</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Clamp on the feedforward longitudinal-acceleration estimate.</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>m/s^2</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim) — set near mu_x*g</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>tires.mu0_long * environment.g = 1.58*9.81 = 15.5 m/s^2</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>The estimate believes the REQUEST. Four wheels at peak (1092 N*m) imply 18.9 m/s^2 = 1.93 g, far past what the tires can deliver, and an over-read here over-predicts rearward load transfer and starves the front — the exact failure the allocator exists to avoid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Left/right load exponent</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.load_exponent</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Exponent on each corner's estimated vertical load when sharing that axle's torque.</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>Sweep 0 -&gt; 1.5 on corner exit; watch inner-wheel slip against outer-wheel margin</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>share_i = Fz_i^p / sum(Fz^p) within an axle. p = 0 is EXACTLY an open differential (which is how the baseline config is built, and a bit-exact check); p = 1 is load-proportional; p &gt; 1 deliberately over-biases the outer wheel. Chosen over the s-diff's steering-angle law because it needs no deadband — the split fades to 50/50 on its own as lateral acceleration goes away — and because it is correct in right-hand corners without any "left is inner" assumption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Minimum wheel share</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.share_min</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Smallest fraction of an axle's torque one wheel may be given.</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>The load estimate clamps a lifted wheel to Fz = 0, which would ask for a 100/0 split the torque limits cannot produce anyway. This keeps a little torque on the unloaded wheel so its speed stays informative to the spin guard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Lateral-accel feedforward fraction</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.ay_ff_frac</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Blend of the kinematic steer estimate into the lateral-acceleration estimate.</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>Step steer — raise until the split leads turn-in without overshooting</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>ay = (1-f)*r*vx + f*vx^2*delta/L. The yaw-rate term is truthful but lags the steering input; the kinematic term has no lag but ignores tire compliance. 0.3 buys phase lead at corner entry for little steady-state cost. (This is torque_vectoring.py's yaw reference reused as a LOAD estimator rather than a closed-loop target — a far lower-risk use of the same expression.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>Lateral accel clamp</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.ay_est_max</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Clamp on the lateral-acceleration estimate used for load transfer.</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>m/s^2</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>r*vx is a product of two estimates; a gyro spike or a vx estimate that has followed four spinning wheels could otherwise saturate the left/right split. 20 m/s^2 (~2 g) is above anything the tires can make, so this never acts in normal running.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>Spin-guard slip threshold</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>kappa_lim</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.kappa_lim</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Slip-ratio magnitude at which the per-corner spin guard starts cutting torque.</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>MagicFormulaTire.kappa_at_peak() at static load — 0.100 front, 0.097 rear</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>Set just below the tire's own peak-force slip, so the guard acts BEFORE more wheel speed starts making less force. Uses |kappa|, so it also catches a wheel locking under regen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Spin-guard gain</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>K_SPIN</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.k_spin</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Proportional cut applied per unit of slip overshoot past kappa_lim.</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>Corner exit at 65-100% throttle; raise until inner-wheel slip is contained</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>h = 1 - k_spin*(|kappa| - kappa_lim)/kappa_lim, floored at spin_floor. Proportional only, no integrator, so there is no gain that needs retuning when the VCU rate changes — which is the standing finding in verify section H.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>Spin-guard floor</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.spin_floor</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Lowest multiplier the spin guard may apply to one corner.</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>Never take a corner to zero: a wheel with no torque gives up its share of drive force AND its slip signal stops being informative. 0.3 keeps both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>Spin-guard release rate</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>controllers.awd.spin_release_rate</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Rate at which a cut corner is allowed back to full torque, per second.</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>TUNED (sim)</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>Deliberately asymmetric — the cut is immediate, the restore is rate limited. That is what stops a wheel cycling between spinning and gripping, and it is why the guard needs no state beyond one multiplier per corner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>SOFTWARE-IN-THE-LOOP (sil/)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>SIL firmware boot time</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>sil.boot_s</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>How long the real firmware is left to boot — bench check (55 ms) plus the ADC settle loop (1 s) — before a maneuver's t = 0, measured on the firmware's own clock.</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — from main.c / initializations.c</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>The firmware's true settle time</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>Read main.c / initializations.c, or instrument the boot</t>
-        </is>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>Too short and the first samples come from an unsettled ADC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Low-speed guard</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>v_eps</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>numerical.v_eps</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Minimum speed used in slip-angle / slip-ratio denominators.</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>Below ~0.5 m/s wheel-slip math is untrustworthy — launches are out of scope until reworked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Wheel-speed guard</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>w_eps</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>numerical.w_eps</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Floor on |wheel speed| when converting a per-motor POWER limit into a torque limit (T_lim = P_peak / max(|omega|, w_eps)).</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>rad/s</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>NUMERICAL GUARD</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>Nothing (numerical)</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>P = T*omega, so at standstill the power limit permits infinite torque. Flooring the divisor caps it at P_peak/w_eps instead, which the per-wheel peak-torque limit then covers. 5 rad/s is ~1.1 m/s of ground speed, below the regen cutoff, so it never binds while the car is actually driving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>GREEN value = confirmed for the CURRENT car/driver (or MEASURED). Black = report car, guess, rules, or sim-tuned. Orange status = placeholder/needs attention. Every row is generated from a params.yaml file — edit the number there, not here.</t>
         </is>
@@ -5486,26 +4432,24 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <mergeCells count="19">
+  <mergeCells count="17">
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A109:J109"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A40:J40"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A92:J92"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A107:J107"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A87:J87"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="B113:J113"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A84:J84"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A66:J66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5986,7 +4930,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>controllers.py</t>
+          <t>sil/vcu_sil.py</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -6023,22 +4967,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>controllers.py</t>
+          <t>sdiff.c (VCU firmware)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>The left/right torque difference: ΔT = ΔT_sdiff, then limits applied.</t>
+          <t>The left/right torque difference the firmware commands: T_RR − T_RL.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Controller output every update</t>
+          <t>Firmware output every VCU cycle</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Commanded over CAN to the AMK inverters; they report actual torque back</t>
+          <t>Commanded over CAN to the inverters as a current per motor</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -6060,27 +5004,27 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>torque_allocator.py output</t>
+          <t>sil/vcu_sil.py</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Final per-wheel torque commands after every limit (peak, regen, power caps).</t>
+          <t>Per-wheel torque the plant receives: the firmware's rear current commands × Kt × gear, mirrored onto the fronts when four wheels are driven.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Base ± ΔT/2, then the limits chain</t>
+          <t>mA command from the firmware, converted each VCU cycle</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>AMK inverters accept torque setpoints and report actuals over CAN</t>
+          <t>Inverters report actual current over CAN</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>What actually gets sent. The limits chain can silently shrink ΔT at high speed — log requested vs delivered on the car.</t>
+          <t>What actually gets applied. Kt is a placeholder, so absolute torque scales with it.</t>
         </is>
       </c>
     </row>

--- a/docs/datasheets/FSAE-Sim Parameters.xlsx
+++ b/docs/datasheets/FSAE-Sim Parameters.xlsx
@@ -11268,12 +11268,12 @@
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Yaw-gyro 1-sigma noise.</t>
+          <t>Yaw-gyro 1-sigma noise per 100 Hz sample. The car's IMU is a VN-100 (team sensor slide 75).</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>0.005236</t>
+          <t>0.0004363</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -11283,17 +11283,17 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — IMU spec</t>
+          <t>PLACEHOLDER — VectorNav VN-100 datasheet value from memory (0.0035 deg/s/sqrt(Hz) x sqrt(50 Hz)); VERIFY against the sheet</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet numbers</t>
+          <t>Confirm the VN-100 noise density on its datasheet</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet</t>
+          <t>VN-100 datasheet: noise density x sqrt(VCU bandwidth)</t>
         </is>
       </c>
       <c r="J225" s="3" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Constant yaw-gyro zero offset.</t>
+          <t>Constant yaw-gyro zero offset left after the VN-100's own calibration.</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>0.001745</t>
+          <t>5.236e-05</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -11335,17 +11335,17 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — uncalibrated bias</t>
+          <t>PLACEHOLDER — VN-100 in-run bias stability (~10 deg/hr) from memory; VERIFY, then calibrate on the car</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet numbers</t>
+          <t>Stationary log on the car</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
-          <t>Chosen IMU's spec sheet, then a stationary calibration on the car</t>
+          <t>VN-100 datasheet bias stability, then a stationary calibration on the car</t>
         </is>
       </c>
       <c r="J226" s="3" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Accelerometer 1-sigma noise (ax, ay channels).</t>
+          <t>Accelerometer 1-sigma noise per 100 Hz sample (ax, ay channels). The car's IMU is a VN-100 (team sensor slide 75).</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -11439,17 +11439,17 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — IMU spec</t>
+          <t>PLACEHOLDER — VN-100 datasheet value from memory (0.14 mg/sqrt(Hz) x sqrt(50 Hz)); VERIFY</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>IMU datasheet</t>
+          <t>Confirm the VN-100 accel noise density on its datasheet</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>Spec sheet</t>
+          <t>VN-100 datasheet: noise density x sqrt(VCU bandwidth)</t>
         </is>
       </c>
       <c r="J228" s="3" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>How often each receiver produces a new speed.</t>
-        </is>
-      </c>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>How often each receiver produces a new speed. SR-17 carries ONE GPS-L10; the model's second receiver (and its bias state) is the DOF doc's provision, not fitted hardware.</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -11704,19 +11704,19 @@
           <t>Hz</t>
         </is>
       </c>
-      <c r="G234" s="5" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — receiver datasheet</t>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT CAR (MoTeC GPS-L10, team sensor slide 79)</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>Receiver datasheet / configured rate</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Sensor slide 79 (MoTeC GPS-L10 datasheet: 10 Hz)</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
